--- a/www/download/COUNTRY.IDN.rpO2.xlsx
+++ b/www/download/COUNTRY.IDN.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Indonésia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>2272.72725159669</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2325.58149802397</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2777.77771550454</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>10000.0002563893</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>7692.30773458784</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>8333.33350296015</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>10000.0001758223</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>9090.90898453412</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>8333.33356401223</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>9090.90905747659</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>10000.0002875486</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>9090.90904036155</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>9090.90895342725</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>9630.849462629</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>10324.520558605</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>87.271</t>
+          <t>0.35900918905289</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>88.91</t>
+          <t>0.490911865781397</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>90.204</t>
+          <t>0.5731837619042</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>90.827</t>
+          <t>0.848225467886721</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>92.114</t>
+          <t>0.402985254970521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>93.321</t>
+          <t>-0.209145376310912</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>93.437</t>
+          <t>-0.258029955588896</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>93.655</t>
+          <t>-0.237154250436899</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>94.323</t>
+          <t>-0.328338670034244</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>94.695</t>
+          <t>-0.256908798299204</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>95.464</t>
+          <t>-0.437231268261014</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>97.88</t>
+          <t>-0.492036618634315</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>103.349</t>
+          <t>-0.533092328006349</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>105.753</t>
+          <t>-0.555403069460046</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>108.203</t>
+          <t>-0.431128551024308</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>29.411</t>
+          <t>1.32830514637194</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.648</t>
+          <t>1.39607908142345</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.685</t>
+          <t>1.41429073351068</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.287</t>
+          <t>1.7861353302706</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>33.271</t>
+          <t>0.972431791707557</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.856</t>
+          <t>0.416287558815368</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35.315</t>
+          <t>0.278177834343364</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.183</t>
+          <t>0.203851978935415</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>33.625</t>
+          <t>0.159745326859826</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>34.679</t>
+          <t>0.0716419139119231</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>36.447</t>
+          <t>0.122172370864585</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>38.129</t>
+          <t>0.153896459236311</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>40.067</t>
+          <t>0.296254786838436</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>40.926</t>
+          <t>0.230564818214242</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>42.189</t>
+          <t>0.615338141348571</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>126800.04</t>
+          <t>2.84678869616152</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>130791.792</t>
+          <t>2.67555700300037</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>130793.751</t>
+          <t>2.98815246534198</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>135652.383</t>
+          <t>3.38154045238393</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>151359.325</t>
+          <t>1.95438675602945</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>150969.555</t>
+          <t>0.939404618514731</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>152843.242</t>
+          <t>0.828964711360008</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>160887.359</t>
+          <t>0.76871131381224</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>164503.981</t>
+          <t>0.588862810691643</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>171431.406</t>
+          <t>0.590695565189235</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>147126.681</t>
+          <t>0.462305555503186</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>138944.74</t>
+          <t>0.393396520769552</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>142588.35</t>
+          <t>0.602905741145204</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>146166.663</t>
+          <t>0.527867192604628</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>149772.086</t>
+          <t>0.959745729714659</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>50845.365</t>
+          <t>880105527984.871</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53343.046</t>
+          <t>1016415140354.31</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>55663.7</t>
+          <t>985801466609.601</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>55335.436</t>
+          <t>837493943814.162</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>63289.03</t>
+          <t>893379793836.382</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>61997.762</t>
+          <t>1072898949916.64</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>64581.67</t>
+          <t>1071285453808.11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>67000.017</t>
+          <t>1202470852979.78</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>65303.248</t>
+          <t>1245973650860.71</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>69112.816</t>
+          <t>1359489917159.54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>60280.812</t>
+          <t>1339454652614.13</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>57540.415</t>
+          <t>1372010407132.8</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>57444.212</t>
+          <t>1261658459893.21</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>58630.515</t>
+          <t>1257221164084.1</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>60602.234</t>
+          <t>992090767462.819</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>135348973961.797</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>149300945726.814</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>135727156113.986</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>117891597331.04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>131790453718.927</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>156588384015.885</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>152953219209.052</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>178622138863.51</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>193135870115.5</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>15.61</t>
+          <t>213974079009.1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>219606627379.451</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>223864358246.161</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>212907839697.493</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>214931681438.448</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>165287352396.749</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>62870935.2497324</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>60768083.3769531</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>57574655.0528275</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>123057442.643337</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>94027762.1447606</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>110512206.78812</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>117368811.574126</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>110240317.895445</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>99202794.0412703</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>33.79</t>
+          <t>104638552.747351</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>96993607.2486685</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>73973033.5366403</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>58278536.4880753</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>48543835.4169962</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>36085134.5960664</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>157545.83533559</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>183446.178473336</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>177325.391514955</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>178464.432411288</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50.89</t>
+          <t>130952.889393141</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>99660.3980816314</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>77711.2435345609</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>83867.9999183971</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>87557.0347219462</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>98233.9079089808</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>78735.9634372982</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>69442.9453644375</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>91626.5595582567</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>102109.712622497</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>116811.384883624</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>368973.789780002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>442478.504727879</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>422738.500516441</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>353248.230464767</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>350895.204789117</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>332356.281963723</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>315653.104547513</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>372316.583403413</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>394429.529831238</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>464861.8855843</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>442744.49672635</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>480614.802423602</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>563249.122579558</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>628031.481610197</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>572368.316065227</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>2.01585216261486</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>1.98123786367214</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>2.16481207732489</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>2.52869141234306</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>1.45371485651098</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>0.587125222591029</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>0.4784279043557</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>0.418902844425382</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>0.284327087798015</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0.262230858417599</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>0.149703470405867</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.0927852293604625</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.193083401305918</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.141029131260669</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.46693141940597</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>48825.329334992</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>53890.5594980207</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>51037.0041872361</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.93</t>
+          <t>26742.7088390645</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>61.66</t>
+          <t>31284.4814312497</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>33934.4750191497</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>33025.3248152127</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>58.49</t>
+          <t>37162.4702735546</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>41722.9342117947</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>49851.9702950525</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>51938.7931268496</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>67691.0060264783</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>80102.8851228427</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>97543.8631333117</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>97844.1351524629</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2272.72725159669</t>
+          <t>4601.97450013849</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2325.58149802397</t>
+          <t>4871.42237631918</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2777.77771550454</t>
+          <t>4152.52487390319</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10000.0002563893</t>
+          <t>3768.09826848051</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7692.30773458784</t>
+          <t>3961.14196394694</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8333.33350296015</t>
+          <t>4765.90635012115</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10000.0001758223</t>
+          <t>4331.08593738369</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9090.90898453412</t>
+          <t>5076.93388132155</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8333.33356401223</t>
+          <t>5743.78185506464</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>9090.90905747659</t>
+          <t>6170.08905875204</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10000.0002875486</t>
+          <t>6025.30071929444</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9090.90904036155</t>
+          <t>5871.20385825889</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>9090.90895342725</t>
+          <t>5313.81282919704</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>9630.849462629</t>
+          <t>5251.70491595661</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>10324.520558605</t>
+          <t>3917.78619178604</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>120926244686.178</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>145635809998.25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>119122560358.745</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>17890306890.3638</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>200485844817.124</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>360999431359.626</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>404019900956.431</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>491378170042.181</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>542155739437.881</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>567283272787.035</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>659698959535.318</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>744133849632.382</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>657776909126.302</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>645433878395.707</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>466651795227.23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>125110775392.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>152783234151.525</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>128704569166.774</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>23891429577.4492</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>210219691385.404</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>384213332985.938</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>423110040563.83</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>505148603741.798</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>548352906965.436</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>570070970405.27</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>689954802998.382</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>778146213550.334</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>687204607962.616</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>666871541665.179</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>479154831817.187</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>-4184530706.03252</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>-7147424153.27499</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>-9582008808.02975</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>-6001122687.08544</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>-9733846568.27978</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>-23213901626.3126</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>-19090139607.399</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>-13770433699.6173</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>-6197167527.55456</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>-2787697618.23539</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>-30255843463.0645</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>-34012363917.9517</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>-29427698836.3131</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>-21437663269.472</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>-12503036589.9577</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>13878.8747485411</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>14522.8688382224</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>13141.9608723208</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>13296.4560008519</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>9719.51288568569</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>7564.09017678402</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>6403.1983059906</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>7203.67592516674</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>7376.89462286225</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>7788.07680914162</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>6927.30914721178</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>6415.96485486947</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>6339.82188416143</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>5992.34829789135</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>5747.1236592458</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>7812.08724200689</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>8294.65798851758</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>7832.3792078724</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>8077.74790083</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>6169.08533676257</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>5749.07861324664</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>4985.85897071282</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>5173.5787163567</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>5497.94531536429</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>5718.50811394006</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>4786.87494373814</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>3742.53994630553</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>3732.71834986204</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>3463.36432826656</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>3329.72484970959</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>54138.457699988</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>61053.5719199881</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>64405.7864399881</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>84.82</t>
+          <t>49432.225459988</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>51848.517879988</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-20.91</t>
+          <t>65346.247149988</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-25.8</t>
+          <t>64404.5237059486</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>65533.6910050178</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-32.83</t>
+          <t>73677.0230267382</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>81394.0512065612</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-43.72</t>
+          <t>93886.8189276342</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-49.2</t>
+          <t>112559.643523315</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>125466.079246621</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-55.54</t>
+          <t>150603.286883368</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-43.11</t>
+          <t>130588.269769243</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>132.83</t>
+          <t>117506393979.35</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>139.61</t>
+          <t>126862847159.445</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>141.43</t>
+          <t>132439093916.23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>178.61</t>
+          <t>215005874997.575</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>97.24</t>
+          <t>174340552304.268</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>266247263565.879</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>282706261509.127</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>263976273686.741</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>274478918461.627</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>317977587539.96</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>320880136095.336</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>302780823310.68</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>261539177092.342</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>243457440719.993</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>61.53</t>
+          <t>158333432705.511</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>284.68</t>
+          <t>52847.5461274449</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>267.56</t>
+          <t>58053.2478633127</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>298.82</t>
+          <t>60132.0333709756</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>338.15</t>
+          <t>36952.9266551684</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>195.44</t>
+          <t>37259.6350323168</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>47322.1241286864</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>48730.331099414</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.87</t>
+          <t>50158.9369691569</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58.89</t>
+          <t>52966.5424989152</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>65882.0796669503</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>78243.8457267915</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>88144.2207202457</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>102583.447461945</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>52.79</t>
+          <t>137567.517918979</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>95.97</t>
+          <t>109126.096597017</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>681770.205</t>
+          <t>233087461452.864</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>737480.132</t>
+          <t>260585028890.065</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>706508.722</t>
+          <t>236884132696.905</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>733675.502</t>
+          <t>186040586453.887</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>568261.348</t>
+          <t>302927752147.09</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>536509.484</t>
+          <t>500571236105.661</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>465863.917</t>
+          <t>568659805073.235</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>484531.29</t>
+          <t>644398435823.557</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>518580.223</t>
+          <t>673185685184.113</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>541516.833</t>
+          <t>786747413664.661</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>456973.521</t>
+          <t>876293278134.317</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>366318.938</t>
+          <t>895571951606.477</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>385774.116</t>
+          <t>813744719558.632</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>366261.954</t>
+          <t>836328670727.72</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>360285.502</t>
+          <t>555406798959.268</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>408192.496</t>
+          <t>1290.91157254311</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>445101.632</t>
+          <t>3000.32405667541</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>429550.943</t>
+          <t>4273.75306901255</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>416003.067</t>
+          <t>12479.2988048195</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>323376.194</t>
+          <t>14588.8828476712</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>248525.374</t>
+          <t>18024.1230213016</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>226130.307</t>
+          <t>15674.1926065346</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>253447.461</t>
+          <t>15374.7540358609</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>248049.63</t>
+          <t>20710.480527823</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>270084.685</t>
+          <t>15511.9715396109</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>252482.502</t>
+          <t>15642.9732008427</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>244635.664</t>
+          <t>24415.4228030691</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>254016.81</t>
+          <t>22882.6317846762</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>245243.31</t>
+          <t>13035.7689643891</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>242465.21</t>
+          <t>21462.173172226</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>880105.528</t>
+          <t>-115581067473.514</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1016415.14</t>
+          <t>-133722181730.62</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>985801.467</t>
+          <t>-104445038780.675</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>837493.944</t>
+          <t>28965288543.6873</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>893379.794</t>
+          <t>-128587199842.822</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1072898.95</t>
+          <t>-234323972539.782</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1071285.454</t>
+          <t>-285953543564.109</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1202470.853</t>
+          <t>-380422162136.816</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1245973.651</t>
+          <t>-398706766722.486</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1359489.917</t>
+          <t>-468769826124.701</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1339454.653</t>
+          <t>-555413142038.98</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1372010.407</t>
+          <t>-592791128295.797</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1261658.46</t>
+          <t>-552205542466.29</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1257221.164</t>
+          <t>-592871230007.727</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>992090.767</t>
+          <t>-397073366253.756</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>155976.45275</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>183352.474</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>185099.45575</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>73327.91787</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>107424.47103</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>116205.18664</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>112488.62669</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>133427.4942</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>154571.72139</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>161614.73025</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>179589.30615</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>240124.54312</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>285485.93308</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>346916.28902</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>368723.7386</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>375790.813</t>
+          <t>0.12431164765859</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>421393.291</t>
+          <t>0.136551161153083</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>413512.445</t>
+          <t>0.157347732027776</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>423110.064</t>
+          <t>0.0842016748048549</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>333406.281</t>
+          <t>0.0997218622344326</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>321719.619</t>
+          <t>0.112682096450463</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>263741.822</t>
+          <t>0.123726130846616</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>270868.476</t>
+          <t>0.136128442734515</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>276586.183</t>
+          <t>0.127062010310847</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>287285.345</t>
+          <t>0.118798736156979</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>238203.418</t>
+          <t>0.134642694138362</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>198238.679</t>
+          <t>0.135824903526462</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>205240.309</t>
+          <t>0.136980894913364</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>204407.734</t>
+          <t>0.139369998316011</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>202470.146</t>
+          <t>0.143597765689627</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>74685.9170336728</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>85768.7808002433</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>85466.0101454388</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>32372.7188251886</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>49043.8056157691</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>52170.1354876091</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>51127.5688411985</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>62032.9060123352</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>74664.3211104431</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>78881.0507419105</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>86065.0585550075</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>114791.24778633</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>135475.775248298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>159754.246728171</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>170476.095240995</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>135348.974</t>
+          <t>122218.850226017</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>149300.946</t>
+          <t>139139.692155326</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>135727.156</t>
+          <t>137534.487450055</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>117891.597</t>
+          <t>55881.1880880761</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>131790.454</t>
+          <t>84495.8385922481</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>156588.384</t>
+          <t>87083.2944607133</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>152953.219</t>
+          <t>82155.3075983676</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>178622.139</t>
+          <t>98587.9465131236</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>193135.87</t>
+          <t>121341.893929067</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>213974.079</t>
+          <t>123970.13623611</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>219606.627</t>
+          <t>129692.577799816</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>223864.358</t>
+          <t>168552.94623058</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>212907.84</t>
+          <t>201540.137830582</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>214931.681</t>
+          <t>234885.642430745</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>165287.352</t>
+          <t>249384.961977804</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>201.59</t>
+          <t>565338.501762948</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>198.12</t>
+          <t>621007.901438404</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>216.48</t>
+          <t>571610.639337541</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>252.87</t>
+          <t>328153.034567267</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>145.37</t>
+          <t>473266.443877202</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>58.71</t>
+          <t>471412.635755221</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>438062.393574817</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>508414.653859651</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>28.43</t>
+          <t>618407.651877284</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>662623.014564901</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>711488.528704662</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>964991.64240088</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>1116617.31158432</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>1303614.24898626</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>1368202.98621071</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>62.871</t>
+          <t>122218.850226017</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>60.768</t>
+          <t>130160.721878188</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>57.575</t>
+          <t>134797.941171521</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>123.057</t>
+          <t>117295.902143358</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>94.028</t>
+          <t>116945.930469545</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>110.512</t>
+          <t>122230.707891744</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>117.369</t>
+          <t>123083.155533244</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>110.24</t>
+          <t>125914.01088163</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>99.203</t>
+          <t>137572.571452366</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>104.639</t>
+          <t>142971.135448487</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>96.994</t>
+          <t>147476.548897103</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>73.973</t>
+          <t>153953.62165738</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>58.279</t>
+          <t>166872.985835487</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>48.544</t>
+          <t>177498.486813025</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>36.085</t>
+          <t>186280.486882258</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>74685.9170336728</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>79973.398473357</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>83068.6002247067</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>68629.6395226062</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>69223.4878698862</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>73506.0442984722</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>76886.2697030478</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>80142.9843630554</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>84835.5291652548</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>90395.4653749394</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>96477.4935537934</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>102550.169774946</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>109567.402333997</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>116937.317715218</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>122877.990778738</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>119103.489973983</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>138689.909524674</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>140978.641889945</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>54373.7439419239</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>78479.4925477519</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>87054.2391092866</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>87225.0898416324</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>106372.165366876</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>120299.053650933</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>128570.74697389</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>147735.525480184</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>198760.90275942</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>233058.123739418</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>279228.578819255</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>294315.026982196</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>408192495830.386</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>445101632482.837</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>429550942890.504</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>416003067089.448</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>323376194236.453</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>248525373836.381</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>226130307339.696</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>253447460910.781</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>248049629614.775</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>270084685426.771</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>252482501622.283</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>244635664071.663</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>254016809550.981</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>245243309752.107</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>242465210461.217</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>681770204678.37</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>737480132187.301</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>706508721501.547</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>733675501863.233</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>568261348298.242</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>536509483561.938</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>465863917382.884</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>484531290196.748</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>518580223015.55</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>541516833183.985</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>456973521171.526</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>366318938385.59</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>385774116176.142</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>366261954129.045</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>360285502159.096</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>375790813413.927</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>421393290856.26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>413512445185.402</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>423110063804.249</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>333406281224.71</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>321719619133.684</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>263741821628.064</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>270868475633.573</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>276586183234.603</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>287285345318.379</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>238203418300.938</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>198238679419.592</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>205240309098.316</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>204407733571.591</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>202470145926.776</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>87271197</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>88910252.0210243</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>90203589.8353118</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>90826739.1939587</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>92114360.1162204</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>93320951</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>93437042.6679519</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>93654956.6096022</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>94322550.2018638</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>94695473.4336958</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>95463852</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>97879767.1210441</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>103349377.053964</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>105753227.039894</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>108202785.041088</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>29411065.6105816</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>30648326.955304</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>32685452.8836112</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>31286762.9587007</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>33270823.1410138</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>32855950.6864638</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35315212.263243</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>35183073.6895503</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>33625209.8336917</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>34679252.9202777</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>36447413.5998256</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>38129208.872769</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>40066868.4692204</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>40926077.3173692</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>42188967.0098096</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>126800040199.903</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>130791791531.132</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>130793750834.673</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>135652382970.267</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>151359324800.349</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>150969554560.976</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>152843242257.524</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>160887359160.359</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>164503980589.901</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>171431405963.774</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>147126680531.104</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>138944740444.118</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>142588349836.274</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>146166663137.177</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>149772086036.291</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>50845365050.5126</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>53343045521.3928</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>55663699525.1387</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>55335436329.601</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>63289030283.2379</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>61997761768.2972</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>64581670110.7665</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>67000017055.0654</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>65303248481.6216</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>69112815842.1906</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>60280811937.4406</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>57540414517.2555</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>57444211606.8405</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>58630514679.0361</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>60602234191.8695</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.133862708237547</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.133862708237547</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.128514223825904</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.135152816633772</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.128149526003451</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.171006830839444</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.165549247462437</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.160804156557938</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.158431611105688</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.156059065653439</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.207353637961907</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.233000924116142</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.228273588657747</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.228273588657747</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.228273588657747</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.295696859929278</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.295696859929278</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.3114356161181</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.312318424954401</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.305843787252101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.307091871869717</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.306444040432225</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.322153545857454</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.330008298570068</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.337863051282682</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.299021406845584</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.279600584627035</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.295540888760317</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.295540888760317</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.295540888760317</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.513297574690318</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.513297574690318</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.502907302913139</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.49538590126897</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.508863829601591</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.464758440147982</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.47086385496248</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.459899440441751</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.454417233181387</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.448935025921022</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.436482098049651</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.430255634113966</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.419042665439079</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.419042665439079</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.419042665439079</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0566899406941814</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0643997535174709</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0620781901604071</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0703749051182925</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0715979891524097</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0829424277174645</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.082612516283083</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0841527025971551</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0782006947582791</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0866247519904517</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0927822374252588</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.0989397228600659</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.0927684627595972</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.0927684627595972</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.0927684627595972</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.225387955959682</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.237009789150174</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.241919450531589</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.25317786226604</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.254701099488972</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.275240379535049</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.268840320941189</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.273826824067002</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.29698568126144</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.288957028372602</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.290555367595629</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.292153706818657</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.281321561177494</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.281321561177494</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.281321561177494</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.66077924620328</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.641447600189498</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.638859502165147</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.619304375472811</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.616558054215761</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.58467433560463</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.591404305632871</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.584877616192986</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.567670766837423</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.567275362494089</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.559519537836255</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.55176371317842</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.568767118920052</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.568767118920052</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.568767118920052</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>461613.99355</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>546448.71254</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>559879.86354</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>212809.83347</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>319134.84753</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>341267.60961</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>334647.75648</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>406241.6321</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>477806.10011</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>498135.18658</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>540977.33985</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>720141.36381</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>849793.95493</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1010597.25217</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1074781.69159</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>241322.3402</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>277829.60168</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>278513.12934</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>110254.93203</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>162975.33114</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>174137.53357</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>169380.39744</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>204960.11188</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>241640.94758</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>252540.88321</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>277428.10328</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>367313.84899</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>434598.26157</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>514114.22125</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>543699.98896</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1284860221.97693</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1355540267.92</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1435586957.90658</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1453125635.01024</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1449814825.64989</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1463501173.80377</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1480376710.52065</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1496236566.85874</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1512417854.28128</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1545191911.31936</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1590299610.3592</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1635814017.64172</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1691586342.68242</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1761628779.98288</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1832545832.63627</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
